--- a/data/trans_orig/P11_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>22738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44500</t>
+          <t>45130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47024</t>
+          <t>44607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>50863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>82410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449564</t>
+          <t>448934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471503</t>
+          <t>471326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420465</t>
+          <t>422882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444423</t>
+          <t>443541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880511</t>
+          <t>879143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>910963</t>
+          <t>910690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30896</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56827</t>
+          <t>56657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70374</t>
+          <t>71758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>106787</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108386</t>
+          <t>108517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153084</t>
+          <t>153342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>678832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>704593</t>
+          <t>705582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>518673</t>
+          <t>518707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555120</t>
+          <t>553736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1207898</t>
+          <t>1207640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1252596</t>
+          <t>1252465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53719</t>
+          <t>54086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83713</t>
+          <t>85254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120330</t>
+          <t>121228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163659</t>
+          <t>165281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184339</t>
+          <t>182952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237002</t>
+          <t>237947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>554955</t>
+          <t>553414</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>584949</t>
+          <t>584582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526085</t>
+          <t>524463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>569414</t>
+          <t>568516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1091410</t>
+          <t>1090465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1144073</t>
+          <t>1145460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76910</t>
+          <t>77449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113909</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133846</t>
+          <t>134951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175092</t>
+          <t>175176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222468</t>
+          <t>223854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276789</t>
+          <t>278898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>405238</t>
+          <t>406166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>442237</t>
+          <t>441698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340550</t>
+          <t>340466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381796</t>
+          <t>380691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>758000</t>
+          <t>755891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>812321</t>
+          <t>810935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100822</t>
+          <t>102858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137341</t>
+          <t>137575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136372</t>
+          <t>136156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175106</t>
+          <t>175821</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248201</t>
+          <t>248842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302059</t>
+          <t>302655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249369</t>
+          <t>249135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285888</t>
+          <t>283852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>228880</t>
+          <t>228165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>267614</t>
+          <t>267830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>488637</t>
+          <t>488041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>542495</t>
+          <t>541854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95134</t>
+          <t>95376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127003</t>
+          <t>126398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>169804</t>
+          <t>170520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>204955</t>
+          <t>203910</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>273679</t>
+          <t>273853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>323268</t>
+          <t>324179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165580</t>
+          <t>166185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197449</t>
+          <t>197207</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137979</t>
+          <t>139024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173130</t>
+          <t>172414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312249</t>
+          <t>311338</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>361838</t>
+          <t>361664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113694</t>
+          <t>113808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140689</t>
+          <t>141850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207440</t>
+          <t>208675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>244306</t>
+          <t>245194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332766</t>
+          <t>330898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>378006</t>
+          <t>376484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69194</t>
+          <t>68033</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96189</t>
+          <t>96075</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>89602</t>
+          <t>88714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>125233</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>165785</t>
+          <t>167307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>211025</t>
+          <t>212893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>552983</t>
+          <t>554337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>642865</t>
+          <t>643076</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>931344</t>
+          <t>933971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1036340</t>
+          <t>1042379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1514374</t>
+          <t>1510899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1655188</t>
+          <t>1649700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2633678</t>
+          <t>2633467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2723560</t>
+          <t>2722206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2342857</t>
+          <t>2336818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2447853</t>
+          <t>2445226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5000553</t>
+          <t>5006041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5141367</t>
+          <t>5144842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37499</t>
+          <t>38283</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>28232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51947</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>50661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79114</t>
+          <t>80764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>413056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434121</t>
+          <t>433658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>378283</t>
+          <t>378831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401966</t>
+          <t>401998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>802455</t>
+          <t>800805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>831774</t>
+          <t>830908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43797</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73879</t>
+          <t>73920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39685</t>
+          <t>41106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69435</t>
+          <t>69894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92164</t>
+          <t>91062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134753</t>
+          <t>132876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>607883</t>
+          <t>607842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>637965</t>
+          <t>637988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>539848</t>
+          <t>539389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>569598</t>
+          <t>568177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1156292</t>
+          <t>1158169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1198881</t>
+          <t>1199983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67049</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104823</t>
+          <t>101548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115331</t>
+          <t>113268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157968</t>
+          <t>156504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192996</t>
+          <t>189326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248392</t>
+          <t>244282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574098</t>
+          <t>577373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611872</t>
+          <t>610589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549988</t>
+          <t>551452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>592625</t>
+          <t>594688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1138485</t>
+          <t>1142595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1193881</t>
+          <t>1197551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70479</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107181</t>
+          <t>107476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143462</t>
+          <t>143133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189185</t>
+          <t>189428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223335</t>
+          <t>225191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284001</t>
+          <t>284036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506502</t>
+          <t>506207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543204</t>
+          <t>543312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>427014</t>
+          <t>426771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472737</t>
+          <t>473066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>945881</t>
+          <t>945846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1006547</t>
+          <t>1004691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95979</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134020</t>
+          <t>133560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183111</t>
+          <t>184324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>228207</t>
+          <t>230267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>290947</t>
+          <t>291049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>350871</t>
+          <t>352237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>293445</t>
+          <t>293905</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331486</t>
+          <t>331565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219593</t>
+          <t>217533</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264689</t>
+          <t>263476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524394</t>
+          <t>523028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>584318</t>
+          <t>584216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105481</t>
+          <t>107292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142468</t>
+          <t>145413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>190432</t>
+          <t>192694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>228883</t>
+          <t>228447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>306467</t>
+          <t>308295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>360215</t>
+          <t>358359</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166318</t>
+          <t>163373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203305</t>
+          <t>201494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125113</t>
+          <t>125549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163564</t>
+          <t>161302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302567</t>
+          <t>304423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356315</t>
+          <t>354487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133898</t>
+          <t>132545</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167141</t>
+          <t>166872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>282851</t>
+          <t>283356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>318294</t>
+          <t>317518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>429240</t>
+          <t>428077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>478003</t>
+          <t>475902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80590</t>
+          <t>80859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113833</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70685</t>
+          <t>71461</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106128</t>
+          <t>105623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>158707</t>
+          <t>160808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207470</t>
+          <t>208633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>596618</t>
+          <t>597889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>691523</t>
+          <t>692568</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1056150</t>
+          <t>1059235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1177238</t>
+          <t>1173836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1684174</t>
+          <t>1681452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1834398</t>
+          <t>1828983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2718164</t>
+          <t>2717119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2813069</t>
+          <t>2811798</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2377206</t>
+          <t>2380608</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2498294</t>
+          <t>2495209</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5129733</t>
+          <t>5135148</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5279957</t>
+          <t>5282679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30706</t>
+          <t>30210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57693</t>
+          <t>55818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>386449</t>
+          <t>385605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404361</t>
+          <t>403779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360055</t>
+          <t>359929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>379198</t>
+          <t>379095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>752767</t>
+          <t>754642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>779754</t>
+          <t>780250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>35083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>63809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>46688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74438</t>
+          <t>75673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89727</t>
+          <t>90842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131300</t>
+          <t>130246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>520624</t>
+          <t>520665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>548602</t>
+          <t>549391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486304</t>
+          <t>485069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514598</t>
+          <t>514054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013916</t>
+          <t>1014970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1055489</t>
+          <t>1054374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60544</t>
+          <t>59493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95965</t>
+          <t>92674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78530</t>
+          <t>78860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115880</t>
+          <t>114379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149917</t>
+          <t>146940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199921</t>
+          <t>195451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>568256</t>
+          <t>571547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603677</t>
+          <t>604728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538087</t>
+          <t>539588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575437</t>
+          <t>575107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1118266</t>
+          <t>1122736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1168270</t>
+          <t>1171247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98741</t>
+          <t>100837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141584</t>
+          <t>142360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128249</t>
+          <t>131887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175512</t>
+          <t>175885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242295</t>
+          <t>243847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>306077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500540</t>
+          <t>499764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543383</t>
+          <t>541287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>470655</t>
+          <t>470282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>517918</t>
+          <t>514280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>984855</t>
+          <t>982214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1045996</t>
+          <t>1044444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,07%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98721</t>
+          <t>98534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137947</t>
+          <t>137602</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>179418</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>226386</t>
+          <t>228264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293607</t>
+          <t>290760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>353507</t>
+          <t>352430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336673</t>
+          <t>337018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375899</t>
+          <t>376086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>267083</t>
+          <t>265205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>314051</t>
+          <t>312604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>614581</t>
+          <t>615658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>674481</t>
+          <t>677328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90464</t>
+          <t>91089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124443</t>
+          <t>126771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>184941</t>
+          <t>183195</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>223476</t>
+          <t>223950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>281512</t>
+          <t>286461</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337223</t>
+          <t>337406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208828</t>
+          <t>206500</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242807</t>
+          <t>242182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153251</t>
+          <t>152777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>191786</t>
+          <t>193532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372775</t>
+          <t>372592</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>428486</t>
+          <t>423537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123972</t>
+          <t>125484</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152899</t>
+          <t>153587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>251250</t>
+          <t>252548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>294559</t>
+          <t>293853</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>386523</t>
+          <t>386618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>437896</t>
+          <t>438320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103316</t>
+          <t>102628</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132243</t>
+          <t>130731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100603</t>
+          <t>101309</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143912</t>
+          <t>142614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213481</t>
+          <t>213057</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>264854</t>
+          <t>264759</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>584514</t>
+          <t>583392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>670850</t>
+          <t>675663</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>963266</t>
+          <t>959073</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1073617</t>
+          <t>1071321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1567702</t>
+          <t>1576319</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1716472</t>
+          <t>1720911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2698780</t>
+          <t>2693967</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2785116</t>
+          <t>2786238</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2448372</t>
+          <t>2450668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2558723</t>
+          <t>2562916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5175146</t>
+          <t>5170707</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5323916</t>
+          <t>5315299</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>54584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>53085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42792</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91891</t>
+          <t>88874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349656</t>
+          <t>345403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386195</t>
+          <t>385623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258658</t>
+          <t>260115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291142</t>
+          <t>291881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>621296</t>
+          <t>624313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>670395</t>
+          <t>672357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47747</t>
+          <t>49840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84741</t>
+          <t>87168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93968</t>
+          <t>93531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100221</t>
+          <t>104928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165759</t>
+          <t>168693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338806</t>
+          <t>336379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375800</t>
+          <t>373707</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417536</t>
+          <t>417973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>468249</t>
+          <t>468044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>769292</t>
+          <t>766358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>834830</t>
+          <t>830123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82284</t>
+          <t>84024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120353</t>
+          <t>121307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110717</t>
+          <t>110176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141997</t>
+          <t>142135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203044</t>
+          <t>201834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253188</t>
+          <t>248184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415985</t>
+          <t>415031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454054</t>
+          <t>452314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>400471</t>
+          <t>400333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431751</t>
+          <t>432292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>825618</t>
+          <t>830622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875762</t>
+          <t>876972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75013</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247301</t>
+          <t>248306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>199972</t>
+          <t>198776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266454</t>
+          <t>263356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244050</t>
+          <t>263019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>501471</t>
+          <t>503249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640485</t>
+          <t>639480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>812773</t>
+          <t>812783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446427</t>
+          <t>449525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512909</t>
+          <t>514105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1099196</t>
+          <t>1097418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1356617</t>
+          <t>1337648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199663</t>
+          <t>197532</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240156</t>
+          <t>242652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234064</t>
+          <t>234382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268261</t>
+          <t>269539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>442936</t>
+          <t>446595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>499150</t>
+          <t>501309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>318746</t>
+          <t>316250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>359239</t>
+          <t>361370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>279644</t>
+          <t>278366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313841</t>
+          <t>313523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>607657</t>
+          <t>605498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>663871</t>
+          <t>660212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>117336</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146398</t>
+          <t>146411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305343</t>
+          <t>307052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>527842</t>
+          <t>533637</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>421331</t>
+          <t>421506</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>770885</t>
+          <t>758663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>77,78%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221767</t>
+          <t>221754</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251195</t>
+          <t>250829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79367</t>
+          <t>73572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301866</t>
+          <t>300157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204489</t>
+          <t>216711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>554043</t>
+          <t>553868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132038</t>
+          <t>131315</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157946</t>
+          <t>158817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>320682</t>
+          <t>320313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>344029</t>
+          <t>343154</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>459629</t>
+          <t>458230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>496860</t>
+          <t>495856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124082</t>
+          <t>123211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149990</t>
+          <t>150713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79063</t>
+          <t>79938</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>102410</t>
+          <t>102779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208260</t>
+          <t>209264</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>245491</t>
+          <t>246890</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>676549</t>
+          <t>670918</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>949686</t>
+          <t>946553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1309506</t>
+          <t>1314973</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1857299</t>
+          <t>1891058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2109118</t>
+          <t>2109545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2856413</t>
+          <t>2774079</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -12179,17 +12179,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2596949</t>
+          <t>2596950</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2507068</t>
+          <t>2510202</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2780205</t>
+          <t>2785837</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1800960</t>
+          <t>1767201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2348753</t>
+          <t>2343286</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4258600</t>
+          <t>4340934</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5005895</t>
+          <t>5005468</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">

--- a/data/trans_orig/P11_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45130</t>
+          <t>45368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44607</t>
+          <t>44365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50863</t>
+          <t>51906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82410</t>
+          <t>83473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448934</t>
+          <t>448696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471326</t>
+          <t>472633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422882</t>
+          <t>423124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>443541</t>
+          <t>444730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879143</t>
+          <t>878080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>910690</t>
+          <t>909647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56657</t>
+          <t>57757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71758</t>
+          <t>71561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106787</t>
+          <t>107084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108517</t>
+          <t>108289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153342</t>
+          <t>155123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>678832</t>
+          <t>677732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>705582</t>
+          <t>704721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>518707</t>
+          <t>518410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>553736</t>
+          <t>553933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1207640</t>
+          <t>1205859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1252465</t>
+          <t>1252693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54086</t>
+          <t>55030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85254</t>
+          <t>85127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121228</t>
+          <t>121148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165281</t>
+          <t>161906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182952</t>
+          <t>183678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237947</t>
+          <t>238543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>553414</t>
+          <t>553541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>584582</t>
+          <t>583638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524463</t>
+          <t>527838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>568516</t>
+          <t>568596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1090465</t>
+          <t>1089869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1145460</t>
+          <t>1144734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77449</t>
+          <t>78087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112981</t>
+          <t>113763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134951</t>
+          <t>132536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175176</t>
+          <t>173727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223854</t>
+          <t>223595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>278898</t>
+          <t>276677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406166</t>
+          <t>405384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>441698</t>
+          <t>441060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340466</t>
+          <t>341915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380691</t>
+          <t>383106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>755891</t>
+          <t>758112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>810935</t>
+          <t>811194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102858</t>
+          <t>101928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137575</t>
+          <t>137909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136156</t>
+          <t>135163</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175821</t>
+          <t>174076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248842</t>
+          <t>250038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302655</t>
+          <t>304898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249135</t>
+          <t>248801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>283852</t>
+          <t>284782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>228165</t>
+          <t>229910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>267830</t>
+          <t>268823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>488041</t>
+          <t>485798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>541854</t>
+          <t>540658</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95376</t>
+          <t>94327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126398</t>
+          <t>125808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>170520</t>
+          <t>169505</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>203910</t>
+          <t>204993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>273853</t>
+          <t>275069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>324179</t>
+          <t>321682</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166185</t>
+          <t>166775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197207</t>
+          <t>198256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139024</t>
+          <t>137941</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172414</t>
+          <t>173429</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>311338</t>
+          <t>313835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>361664</t>
+          <t>360448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113808</t>
+          <t>113949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141850</t>
+          <t>140524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208675</t>
+          <t>209097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>245194</t>
+          <t>244498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>330898</t>
+          <t>331238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376484</t>
+          <t>377332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68033</t>
+          <t>69359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96075</t>
+          <t>95934</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88714</t>
+          <t>89410</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125233</t>
+          <t>124811</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>167307</t>
+          <t>166459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212893</t>
+          <t>212553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,09%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>554337</t>
+          <t>553244</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>643076</t>
+          <t>639974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>933971</t>
+          <t>938814</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1042379</t>
+          <t>1044684</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1510899</t>
+          <t>1508456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1649700</t>
+          <t>1648796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2633467</t>
+          <t>2636569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2722206</t>
+          <t>2723299</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2336818</t>
+          <t>2334513</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2445226</t>
+          <t>2440383</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5006041</t>
+          <t>5006945</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5144842</t>
+          <t>5147285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17681</t>
+          <t>17650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38283</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51399</t>
+          <t>51801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50661</t>
+          <t>50775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80764</t>
+          <t>79521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413056</t>
+          <t>414289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433658</t>
+          <t>433689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>378831</t>
+          <t>378429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401998</t>
+          <t>402319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>800805</t>
+          <t>802048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>830908</t>
+          <t>830794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43774</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73920</t>
+          <t>74506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69894</t>
+          <t>70818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91062</t>
+          <t>93172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132876</t>
+          <t>135383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>607842</t>
+          <t>607256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>637988</t>
+          <t>639596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>539389</t>
+          <t>538465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>568177</t>
+          <t>567734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1158169</t>
+          <t>1155662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1199983</t>
+          <t>1197873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68332</t>
+          <t>68030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>104490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113268</t>
+          <t>113282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156504</t>
+          <t>155790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189326</t>
+          <t>192856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244282</t>
+          <t>248618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577373</t>
+          <t>574431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610589</t>
+          <t>610891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>551452</t>
+          <t>552166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>594688</t>
+          <t>594674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1142595</t>
+          <t>1138259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1197551</t>
+          <t>1194021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>69511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>106876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143133</t>
+          <t>144510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189428</t>
+          <t>191007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225191</t>
+          <t>219892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284036</t>
+          <t>281633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506207</t>
+          <t>506807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543312</t>
+          <t>544172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426771</t>
+          <t>425192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473066</t>
+          <t>471689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>945846</t>
+          <t>948249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1004691</t>
+          <t>1009990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95900</t>
+          <t>97254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133560</t>
+          <t>134890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184324</t>
+          <t>185819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230267</t>
+          <t>230070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>291049</t>
+          <t>292423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352237</t>
+          <t>351353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>293905</t>
+          <t>292575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331565</t>
+          <t>330211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>217533</t>
+          <t>217730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263476</t>
+          <t>261981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>523028</t>
+          <t>523912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>584216</t>
+          <t>582842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107292</t>
+          <t>105111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145413</t>
+          <t>142823</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>192694</t>
+          <t>191747</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>228447</t>
+          <t>229882</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>308295</t>
+          <t>308804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>358359</t>
+          <t>362075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163373</t>
+          <t>165963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201494</t>
+          <t>203675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125549</t>
+          <t>124114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>161302</t>
+          <t>162249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>304423</t>
+          <t>300707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354487</t>
+          <t>353978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132545</t>
+          <t>133462</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166872</t>
+          <t>167675</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>283356</t>
+          <t>285242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>317518</t>
+          <t>320206</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>428077</t>
+          <t>430674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475902</t>
+          <t>476676</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>80056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115186</t>
+          <t>114269</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71461</t>
+          <t>68773</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105623</t>
+          <t>103737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>160808</t>
+          <t>160034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>208633</t>
+          <t>206036</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>597889</t>
+          <t>597213</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>692568</t>
+          <t>692784</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1059235</t>
+          <t>1054956</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1173836</t>
+          <t>1165572</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1681452</t>
+          <t>1686514</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1828983</t>
+          <t>1834573</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2717119</t>
+          <t>2716903</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2811798</t>
+          <t>2812474</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2380608</t>
+          <t>2388872</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2495209</t>
+          <t>2499488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5135148</t>
+          <t>5129558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5282679</t>
+          <t>5277617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29100</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>34499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55818</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>385605</t>
+          <t>385628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403779</t>
+          <t>404154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>359929</t>
+          <t>361256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>379095</t>
+          <t>379626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>754642</t>
+          <t>752558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>780250</t>
+          <t>779277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>62940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46688</t>
+          <t>47703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75673</t>
+          <t>75871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90842</t>
+          <t>91182</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130246</t>
+          <t>129480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>520665</t>
+          <t>521534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>549391</t>
+          <t>548098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485069</t>
+          <t>484871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514054</t>
+          <t>513039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1014970</t>
+          <t>1015736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1054374</t>
+          <t>1054034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59493</t>
+          <t>59350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92674</t>
+          <t>94044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78860</t>
+          <t>79759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114379</t>
+          <t>114735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146940</t>
+          <t>148749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195451</t>
+          <t>196342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>571547</t>
+          <t>570177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>604728</t>
+          <t>604871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539588</t>
+          <t>539232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575107</t>
+          <t>574208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1122736</t>
+          <t>1121845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1171247</t>
+          <t>1169438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100837</t>
+          <t>101996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142360</t>
+          <t>142940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131887</t>
+          <t>130581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175885</t>
+          <t>174308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>243847</t>
+          <t>243211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>306077</t>
+          <t>305538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499764</t>
+          <t>499184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>541287</t>
+          <t>540128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>470282</t>
+          <t>471859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>514280</t>
+          <t>515586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>982214</t>
+          <t>982753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1044444</t>
+          <t>1045080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98534</t>
+          <t>99557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137602</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>181156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>228264</t>
+          <t>226510</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>290760</t>
+          <t>292125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352430</t>
+          <t>353187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337018</t>
+          <t>337439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>376086</t>
+          <t>375063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>265205</t>
+          <t>266959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312604</t>
+          <t>312313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>615658</t>
+          <t>614901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>677328</t>
+          <t>675963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91089</t>
+          <t>90402</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126771</t>
+          <t>125348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183195</t>
+          <t>183594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>223950</t>
+          <t>223602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>286461</t>
+          <t>285372</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337406</t>
+          <t>339961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206500</t>
+          <t>207923</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242182</t>
+          <t>242869</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>152777</t>
+          <t>153125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193532</t>
+          <t>193133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372592</t>
+          <t>370037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>423537</t>
+          <t>424626</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125484</t>
+          <t>124374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153587</t>
+          <t>152688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252548</t>
+          <t>249872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>293853</t>
+          <t>292898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>386618</t>
+          <t>387140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>438320</t>
+          <t>437822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,21%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102628</t>
+          <t>103527</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130731</t>
+          <t>131841</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>101309</t>
+          <t>102264</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142614</t>
+          <t>145290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213057</t>
+          <t>213555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>264759</t>
+          <t>264237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>583392</t>
+          <t>585906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>675663</t>
+          <t>673772</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>959073</t>
+          <t>957490</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1071321</t>
+          <t>1065099</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1576319</t>
+          <t>1570059</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1720911</t>
+          <t>1711007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2693967</t>
+          <t>2695858</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2786238</t>
+          <t>2783724</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2450668</t>
+          <t>2456890</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2562916</t>
+          <t>2564499</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5170707</t>
+          <t>5180611</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5315299</t>
+          <t>5321559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>33494</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54584</t>
+          <t>52600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34745</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53085</t>
+          <t>63675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40830</t>
+          <t>55391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88874</t>
+          <t>104327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>373406</t>
+          <t>374299</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345403</t>
+          <t>355193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385623</t>
+          <t>388572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278455</t>
+          <t>319098</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260115</t>
+          <t>298837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291881</t>
+          <t>334873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>651860</t>
+          <t>693397</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>624313</t>
+          <t>665978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>672357</t>
+          <t>714914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64925</t>
+          <t>74466</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49840</t>
+          <t>55304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87168</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72564</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43460</t>
+          <t>61227</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93531</t>
+          <t>94821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>137489</t>
+          <t>151852</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104928</t>
+          <t>127593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168693</t>
+          <t>177913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>358622</t>
+          <t>402424</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336379</t>
+          <t>381120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373707</t>
+          <t>421586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>438940</t>
+          <t>423697</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417973</t>
+          <t>406262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>468044</t>
+          <t>439856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>797562</t>
+          <t>826121</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>766358</t>
+          <t>800060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>830123</t>
+          <t>850380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100646</t>
+          <t>113833</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84024</t>
+          <t>94966</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121307</t>
+          <t>136641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>124860</t>
+          <t>142051</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110176</t>
+          <t>126132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142135</t>
+          <t>163167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>225506</t>
+          <t>255884</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201834</t>
+          <t>231466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248184</t>
+          <t>283581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>435692</t>
+          <t>507004</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415031</t>
+          <t>484196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452314</t>
+          <t>525871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>417608</t>
+          <t>480088</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>400333</t>
+          <t>458972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432292</t>
+          <t>496007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>853300</t>
+          <t>987092</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>830622</t>
+          <t>959395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>876972</t>
+          <t>1011510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>171340</t>
+          <t>183471</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>160982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248306</t>
+          <t>209567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>241446</t>
+          <t>254177</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198776</t>
+          <t>234910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263356</t>
+          <t>274258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>412786</t>
+          <t>437648</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>263019</t>
+          <t>407563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>503249</t>
+          <t>469305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>716446</t>
+          <t>517146</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>639480</t>
+          <t>491050</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>812783</t>
+          <t>539635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>471435</t>
+          <t>482709</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449525</t>
+          <t>462628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>514105</t>
+          <t>501976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1187881</t>
+          <t>999856</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1097418</t>
+          <t>968199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337648</t>
+          <t>1029941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>219732</t>
+          <t>228651</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>197532</t>
+          <t>204718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242652</t>
+          <t>250380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>251831</t>
+          <t>279362</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234382</t>
+          <t>259583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>269539</t>
+          <t>298129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>471563</t>
+          <t>508013</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>446595</t>
+          <t>480120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>501309</t>
+          <t>536933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>339170</t>
+          <t>378077</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>316250</t>
+          <t>356348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361370</t>
+          <t>402010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>296074</t>
+          <t>329493</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278366</t>
+          <t>310726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313523</t>
+          <t>349272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>635244</t>
+          <t>707571</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>605498</t>
+          <t>678651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>660212</t>
+          <t>735464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558902</t>
+          <t>606728</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558902</t>
+          <t>606728</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558902</t>
+          <t>606728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106807</t>
+          <t>1215584</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106807</t>
+          <t>1215584</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106807</t>
+          <t>1215584</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>131479</t>
+          <t>142202</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117336</t>
+          <t>125667</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146411</t>
+          <t>158041</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>412730</t>
+          <t>228364</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307052</t>
+          <t>212440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>533637</t>
+          <t>242691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>544209</t>
+          <t>370566</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>421506</t>
+          <t>348394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>758663</t>
+          <t>393039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236686</t>
+          <t>264878</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221754</t>
+          <t>249039</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250829</t>
+          <t>281413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>194479</t>
+          <t>209454</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73572</t>
+          <t>195127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300157</t>
+          <t>225378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>431165</t>
+          <t>474332</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216711</t>
+          <t>451859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>553868</t>
+          <t>496504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607209</t>
+          <t>437818</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607209</t>
+          <t>437818</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607209</t>
+          <t>437818</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>844898</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>844898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>844898</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>157195</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131315</t>
+          <t>143541</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158817</t>
+          <t>171917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>332555</t>
+          <t>360339</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>320313</t>
+          <t>346476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>343154</t>
+          <t>372667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>477656</t>
+          <t>517534</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>458230</t>
+          <t>496369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>495856</t>
+          <t>535820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>136927</t>
+          <t>151999</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123211</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150713</t>
+          <t>165653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>90537</t>
+          <t>101160</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79938</t>
+          <t>88832</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>102779</t>
+          <t>115023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>227464</t>
+          <t>253159</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209264</t>
+          <t>234873</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>246890</t>
+          <t>274324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282028</t>
+          <t>309194</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282028</t>
+          <t>309194</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282028</t>
+          <t>309194</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423092</t>
+          <t>461499</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423092</t>
+          <t>461499</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423092</t>
+          <t>461499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705120</t>
+          <t>770693</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705120</t>
+          <t>770693</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705120</t>
+          <t>770693</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>859805</t>
+          <t>933312</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>670918</t>
+          <t>875133</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>946553</t>
+          <t>985944</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1470732</t>
+          <t>1385094</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1314973</t>
+          <t>1331342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1891058</t>
+          <t>1435380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2330537</t>
+          <t>2318406</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2109545</t>
+          <t>2244434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2774079</t>
+          <t>2401930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2596950</t>
+          <t>2595828</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2510202</t>
+          <t>2543196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2785837</t>
+          <t>2654007</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2187527</t>
+          <t>2345700</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1767201</t>
+          <t>2295414</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2343286</t>
+          <t>2399452</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4784476</t>
+          <t>4941528</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4340934</t>
+          <t>4858004</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5005468</t>
+          <t>5015500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
